--- a/output/multi_factor_reports/multi_factor_test_report_P10.xlsx
+++ b/output/multi_factor_reports/multi_factor_test_report_P10.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新建文件夹\qqq\output\multi_factor_reports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\qqq\output\multi_factor_reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DE49D8-DDA3-4CB9-A95B-DD613A48D095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1A7F1E5-3F77-42E7-A7CF-45652D6D076F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10552,6 +10552,5254 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>alpha001</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$A$2:$A$76</c:f>
+              <c:strCache>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>2023-01-18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2023-02-01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-02-15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023-03-02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023-03-16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023-03-30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2023-04-14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2023-04-28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2023-05-12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2023-05-26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023-06-12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2023-06-27</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2023-07-12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2023-07-26</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2023-08-09</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2023-08-23</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2023-09-07</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2023-09-21</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023-10-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2023-10-19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2023-11-02</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2023-11-16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2023-12-01</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023-12-15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024-01-02</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024-01-17</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2024-01-31</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2024-02-14</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2024-02-29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024-03-14</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2024-03-28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2024-04-12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2024-04-26</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024-05-10</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024-05-24</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024-06-10</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2024-06-25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2024-07-10</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2024-07-24</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2024-08-07</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2024-08-21</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2024-09-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2024-09-19</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2024-10-03</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2024-10-17</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2024-10-31</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2024-11-14</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2024-11-29</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2024-12-13</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024-12-30</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025-01-15</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2025-01-30</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2025-02-13</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2025-02-28</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2025-03-14</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2025-03-28</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2025-04-11</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2025-04-28</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2025-05-12</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2025-05-27</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2025-06-10</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2025-06-25</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2025-07-10</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2025-07-24</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2025-08-07</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2025-08-21</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2025-09-05</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2025-09-19</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2025-10-03</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2025-10-17</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2025-10-31</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2025-11-14</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2025-12-01</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2025-12-15</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2025-12-30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>factor_LE_cum_ret!$B$2:$B$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="75"/>
+                <c:pt idx="2">
+                  <c:v>-1.2445193451357641E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-3.4949794504196552E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4.8460325662799793E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-6.0640216805441287E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-5.090196187547058E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-6.9641739961686544E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-4.7857539159158913E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4.7768523717261813E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-6.1872574842786188E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-6.7072663942592037E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-7.0362919946359459E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-7.6231190880279742E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-7.6465257091477001E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-8.3972719690567299E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-9.4148668180776163E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-8.8314938489046924E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-9.9028658530193603E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.1063959926826297</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.115781385442253</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-9.9116704341860595E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-8.5776813333073521E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-9.6217430002655813E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-8.3517832153874649E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-7.5870002083683441E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-9.1108396179901074E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-8.7633815863249254E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-9.6384363531689332E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-8.77364991959656E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-9.2600866783453917E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-9.6032776972070022E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-9.6368637488491893E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-0.1150404727917531</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-0.1099684358568559</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-0.122610572595205</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0.12945232241109569</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-0.13601941967224801</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.13178838284541131</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-0.15281259753964599</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-0.1548163428667193</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-0.1735461587877121</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-0.1631745534835084</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-0.17150754631579901</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-0.17455283779345049</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-0.18901239754607849</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-0.19226617241769611</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-0.2079762907698379</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-0.20769740436717679</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-0.19900751802672381</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-0.20016381036872799</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-0.211452124193553</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-0.2125159941720591</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-0.21629507726369171</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-0.2103052488496934</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-0.202148096363331</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-0.21641891018631429</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-0.2094073073565561</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-0.20717656232944129</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-0.2095223959998882</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-0.2041595743127311</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-0.19769828509685419</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-0.1812086055247325</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-0.18050331046204929</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-0.17673619628803611</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-0.18057930349914239</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-0.17938113263202499</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-0.17884209609985829</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-0.16320957266919239</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-0.16323711630822421</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-0.16198408160257441</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>-0.16117883031322361</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-0.14353266916729779</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-0.14593320635348489</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-0.1168700238719996</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-0C4C-4E74-A26C-F7D819994232}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>alpha002</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$A$2:$A$76</c:f>
+              <c:strCache>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>2023-01-18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2023-02-01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-02-15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023-03-02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023-03-16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023-03-30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2023-04-14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2023-04-28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2023-05-12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2023-05-26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023-06-12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2023-06-27</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2023-07-12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2023-07-26</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2023-08-09</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2023-08-23</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2023-09-07</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2023-09-21</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023-10-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2023-10-19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2023-11-02</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2023-11-16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2023-12-01</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023-12-15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024-01-02</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024-01-17</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2024-01-31</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2024-02-14</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2024-02-29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024-03-14</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2024-03-28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2024-04-12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2024-04-26</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024-05-10</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024-05-24</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024-06-10</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2024-06-25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2024-07-10</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2024-07-24</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2024-08-07</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2024-08-21</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2024-09-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2024-09-19</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2024-10-03</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2024-10-17</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2024-10-31</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2024-11-14</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2024-11-29</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2024-12-13</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024-12-30</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025-01-15</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2025-01-30</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2025-02-13</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2025-02-28</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2025-03-14</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2025-03-28</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2025-04-11</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2025-04-28</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2025-05-12</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2025-05-27</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2025-06-10</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2025-06-25</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2025-07-10</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2025-07-24</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2025-08-07</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2025-08-21</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2025-09-05</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2025-09-19</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2025-10-03</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2025-10-17</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2025-10-31</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2025-11-14</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2025-12-01</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2025-12-15</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2025-12-30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>factor_LE_cum_ret!$C$2:$C$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>-1.817895670788405E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.403526414299086E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-4.1386862346824982E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.390499649034596E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-3.9226113099165023E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-3.8230434110507527E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.1516318743363367E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-3.7845437352602478E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-4.6501221173059881E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4.3548798180322201E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-4.1447196130632517E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-4.0814368154951763E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-3.6138142261081252E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-4.6051999459194359E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-4.2013564661523388E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-4.8766226240723458E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-3.9755856257523869E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-3.4258629980466797E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-3.6515785242108301E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-4.8633165074786988E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-5.7069867517999577E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-5.4733370299362212E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-6.3219736889095324E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-6.3818486559274468E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-6.4163106295664574E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-5.8857544425811932E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-3.3210846059347772E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-3.4984622870259052E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-2.925306175519948E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-3.2735648467428491E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-3.5689492919561687E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-2.0042567731113681E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-2.1595804506227449E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-3.0337637542825591E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-3.801781157309625E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-4.0061341197013538E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-2.0636035987189438E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.002119303778271E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.759371084350558E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.235780921764928E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8.1718754586912468E-3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.0856708948832731E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3.1743168798978871E-3</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2.993525971582534E-3</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.9653927952876264E-3</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.9057812424748691E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>5.5730958687887364E-3</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>1.18639192687211E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.281586986412853E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1.8340602886439239E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1.605600979778754E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2.1886560597150329E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>3.4607813938940519E-3</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-1.0466218923585241E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-9.8628336501777047E-3</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1.15360776872333E-2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-1.58821445407531E-3</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-8.6197589157277488E-4</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-8.2560121122597918E-3</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-8.7383535968331705E-3</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-2.0511276108664211E-2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-2.2414643454071629E-2</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-1.7712048791093778E-2</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-9.8126742620574525E-3</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-9.2983388177371173E-3</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-5.8885012358080857E-3</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-1.9088232640389611E-3</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-1.2388486740991239E-2</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-6.2243892259638001E-3</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-4.8561789473694486E-3</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>4.3521228180101179E-3</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1.16635912252927E-3</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2.4985037429359198E-3</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>3.077555906633167E-3</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-2.2253844027109171E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-0C4C-4E74-A26C-F7D819994232}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>alpha003</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$A$2:$A$76</c:f>
+              <c:strCache>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>2023-01-18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2023-02-01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-02-15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023-03-02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023-03-16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023-03-30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2023-04-14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2023-04-28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2023-05-12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2023-05-26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023-06-12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2023-06-27</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2023-07-12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2023-07-26</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2023-08-09</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2023-08-23</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2023-09-07</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2023-09-21</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023-10-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2023-10-19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2023-11-02</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2023-11-16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2023-12-01</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023-12-15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024-01-02</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024-01-17</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2024-01-31</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2024-02-14</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2024-02-29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024-03-14</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2024-03-28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2024-04-12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2024-04-26</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024-05-10</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024-05-24</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024-06-10</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2024-06-25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2024-07-10</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2024-07-24</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2024-08-07</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2024-08-21</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2024-09-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2024-09-19</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2024-10-03</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2024-10-17</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2024-10-31</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2024-11-14</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2024-11-29</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2024-12-13</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024-12-30</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025-01-15</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2025-01-30</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2025-02-13</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2025-02-28</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2025-03-14</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2025-03-28</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2025-04-11</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2025-04-28</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2025-05-12</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2025-05-27</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2025-06-10</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2025-06-25</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2025-07-10</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2025-07-24</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2025-08-07</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2025-08-21</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2025-09-05</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2025-09-19</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2025-10-03</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2025-10-17</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2025-10-31</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2025-11-14</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2025-12-01</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2025-12-15</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2025-12-30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>factor_LE_cum_ret!$D$2:$D$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>9.0953748572537574E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.8013906315627111E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5.8410994405324601E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1.5279136017063429E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>7.1945946908567038E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>7.7210517622234853E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.1992349487813581E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-8.1120556808514932E-3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1.2958571944483349E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1.5172920264819201E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-7.95494399866159E-3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1.135997846113534E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-2.0002735017187519E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-3.0838388889708471E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-2.274374791973699E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-3.6397854160995717E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-3.6730582904893512E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-2.8550856341048592E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-2.635224616562026E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-2.1218741006695189E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-4.8851572176222713E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-4.2587658068250822E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-3.6342496080018598E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-3.0867175875742059E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-2.8226643743074039E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-2.8194301011590591E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-4.4975318001529763E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-4.7103292162142707E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-4.4561414710909242E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-4.1781332721475217E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-4.4731513646555032E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-3.9446213845247817E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-4.553712287033318E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-3.8685637307365073E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-3.7660167752905482E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-2.3779749326548919E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-3.3134552823086971E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-3.0033891329696919E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-1.202389956308381E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-3.0205857171276111E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-2.7540526240727229E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-3.2978610920494367E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-3.1383220158021641E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-3.5194407305513042E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-4.5804395127780673E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-4.4210997069071722E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-5.167757424124475E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-6.6805829549215545E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-7.2478506537876686E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-7.2854357016589155E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-7.1240450085625295E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-6.8423668633646462E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-5.9048242796664867E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-5.4836391994919631E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-5.2121306417156177E-2</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-6.5561438796566729E-2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-5.7126827999522067E-2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-5.8589186557898347E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-7.2748537597527752E-2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-6.5124331128552648E-2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-7.0698020198322276E-2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-7.6442287596278802E-2</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-7.7555457724992283E-2</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-7.9854466410347325E-2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-9.3477456116779489E-2</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-9.1317082395716787E-2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-0.1120952741424063</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-0.1127734555026398</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-0.1191570949318173</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-0.13379826458351221</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-0.12566693281159061</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>-0.1363714418471054</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-0.1247738484182872</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-0.1286466352113915</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-0.12924462457897279</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-0C4C-4E74-A26C-F7D819994232}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>alpha004</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$A$2:$A$76</c:f>
+              <c:strCache>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>2023-01-18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2023-02-01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-02-15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023-03-02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023-03-16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023-03-30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2023-04-14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2023-04-28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2023-05-12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2023-05-26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023-06-12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2023-06-27</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2023-07-12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2023-07-26</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2023-08-09</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2023-08-23</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2023-09-07</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2023-09-21</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023-10-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2023-10-19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2023-11-02</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2023-11-16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2023-12-01</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023-12-15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024-01-02</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024-01-17</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2024-01-31</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2024-02-14</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2024-02-29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024-03-14</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2024-03-28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2024-04-12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2024-04-26</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024-05-10</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024-05-24</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024-06-10</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2024-06-25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2024-07-10</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2024-07-24</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2024-08-07</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2024-08-21</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2024-09-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2024-09-19</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2024-10-03</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2024-10-17</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2024-10-31</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2024-11-14</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2024-11-29</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2024-12-13</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024-12-30</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025-01-15</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2025-01-30</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2025-02-13</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2025-02-28</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2025-03-14</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2025-03-28</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2025-04-11</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2025-04-28</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2025-05-12</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2025-05-27</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2025-06-10</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2025-06-25</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2025-07-10</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2025-07-24</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2025-08-07</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2025-08-21</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2025-09-05</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2025-09-19</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2025-10-03</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2025-10-17</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2025-10-31</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2025-11-14</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2025-12-01</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2025-12-15</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2025-12-30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>factor_LE_cum_ret!$E$2:$E$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>-2.8928269371202301E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-3.7005965137982821E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-4.9126117647477763E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.4395322501119772E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4.8317264946074252E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-3.7736888602276419E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-5.3416706820107129E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-7.8725816026835926E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.102695275532195</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.10057610916714781</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-8.7918968071771131E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-8.3558647137241149E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-9.0936565102635813E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-9.2998385503833325E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-9.8762505463866335E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.10549276876255741</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-9.7568515634077424E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-9.6080607007269503E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-9.8534463860774801E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.11283738931790641</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.13792042580349301</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.13966480179324869</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.14052476092475041</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-0.13184174014306699</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.13590224364020589</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-0.1402930014839249</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.15493742802820251</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.147819067771045</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-0.1471816917127364</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-0.13599836276468441</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-0.13356102433296271</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-0.1317352249021958</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-0.1313082291414043</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-0.1478381385180014</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-0.13658645325628779</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-0.14409467140857829</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0.1410326646280102</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-0.1084792507183646</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.13645732342297681</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-0.12603126122466091</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-0.1176896769385599</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-0.108764991170786</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-0.1150991644992313</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-0.1128671432303817</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-9.8727569071206722E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-0.1167540519543102</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-0.11912760182814359</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-9.386740520118686E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-9.878819374802883E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-9.9607317131299999E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-0.10868222726821609</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-0.1236195292772346</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-0.12419985976004271</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-0.14207418289995191</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-0.1423795332950909</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-0.14339584800257091</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-0.14806505702707809</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-0.18797362170341941</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-0.19023248313627639</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-0.1781215913606522</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-0.1881267659490877</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-0.1876101257875491</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-0.18328281532545471</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-0.1815973902773742</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-0.1704657845140074</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-0.16251387368098899</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-0.16891439267812139</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-0.17387078378065141</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-0.17794945855321331</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-0.1855395888202469</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-0.17860563715670491</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>-0.17647743014707601</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-0.1935933622107591</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-0.1826092158187641</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-0.16505835904325941</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-0C4C-4E74-A26C-F7D819994232}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>alpha005</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$A$2:$A$76</c:f>
+              <c:strCache>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>2023-01-18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2023-02-01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-02-15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023-03-02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023-03-16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023-03-30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2023-04-14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2023-04-28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2023-05-12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2023-05-26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023-06-12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2023-06-27</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2023-07-12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2023-07-26</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2023-08-09</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2023-08-23</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2023-09-07</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2023-09-21</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023-10-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2023-10-19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2023-11-02</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2023-11-16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2023-12-01</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023-12-15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024-01-02</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024-01-17</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2024-01-31</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2024-02-14</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2024-02-29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024-03-14</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2024-03-28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2024-04-12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2024-04-26</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024-05-10</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024-05-24</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024-06-10</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2024-06-25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2024-07-10</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2024-07-24</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2024-08-07</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2024-08-21</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2024-09-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2024-09-19</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2024-10-03</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2024-10-17</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2024-10-31</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2024-11-14</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2024-11-29</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2024-12-13</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024-12-30</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025-01-15</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2025-01-30</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2025-02-13</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2025-02-28</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2025-03-14</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2025-03-28</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2025-04-11</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2025-04-28</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2025-05-12</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2025-05-27</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2025-06-10</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2025-06-25</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2025-07-10</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2025-07-24</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2025-08-07</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2025-08-21</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2025-09-05</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2025-09-19</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2025-10-03</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2025-10-17</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2025-10-31</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2025-11-14</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2025-12-01</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2025-12-15</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2025-12-30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>factor_LE_cum_ret!$F$2:$F$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>-3.6086371999875189E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.62427256038207E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-4.7952070538601177E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.7314840742808451E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-5.495461298991422E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-6.2981271922174842E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-7.2817866126483999E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-9.0483118020918796E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.1021372996281226</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.1123223410514089</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.10965390790320351</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.1018022846217866</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-9.185809410969481E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-8.0041118780177056E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-8.9497856752606353E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-9.1155234003329144E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-6.8403169929344698E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-5.6229892591712627E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-5.5190301349783422E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-5.6882694327725081E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-6.0079970081981293E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-6.453918567396133E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-7.5497327075720988E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-6.9253810827258122E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-8.0875405187802674E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-9.6597968049371596E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.11505926750131661</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.1203754717903619</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-0.1200689646943839</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-0.1224767832823874</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-0.13616272712545729</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-0.14259971310222719</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-0.14774047645441241</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-0.16031528694369759</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-0.15937833266053561</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-0.1512020901173646</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0.14643451492364171</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-0.122223305496532</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.14106541444618301</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-0.13017762250920881</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-0.11465002658541371</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-0.1039562007940374</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-0.1092752374128285</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-0.1082712090434967</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-9.1023426624242121E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-9.4168892486208966E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-9.3103106658369406E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-7.7903745225042065E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-8.02151772295151E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-7.5985999663261472E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-8.7671319200761544E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-9.9132391111371287E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-9.9835632193056356E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-0.1220952133878896</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-0.1191137301635866</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-0.117999988422297</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-0.13660173649919991</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-0.15811997014865101</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-0.16463588884314759</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-0.16398209482928799</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-0.16658875229285819</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-0.17220004678856299</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-0.19148118374358661</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-0.186999299819502</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-0.18518797989777369</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-0.18574673030703401</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-0.18428262391963379</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-0.1962089711438415</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-0.20682164344929499</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-0.2055270214201628</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-0.21261444029362009</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>-0.2103235889374839</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-0.21410801460792711</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-0.20467115776965439</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-0.21566685466207319</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-0C4C-4E74-A26C-F7D819994232}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>alpha006</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$A$2:$A$76</c:f>
+              <c:strCache>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>2023-01-18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2023-02-01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-02-15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023-03-02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023-03-16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023-03-30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2023-04-14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2023-04-28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2023-05-12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2023-05-26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023-06-12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2023-06-27</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2023-07-12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2023-07-26</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2023-08-09</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2023-08-23</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2023-09-07</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2023-09-21</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023-10-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2023-10-19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2023-11-02</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2023-11-16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2023-12-01</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023-12-15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024-01-02</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024-01-17</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2024-01-31</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2024-02-14</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2024-02-29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024-03-14</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2024-03-28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2024-04-12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2024-04-26</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024-05-10</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024-05-24</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024-06-10</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2024-06-25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2024-07-10</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2024-07-24</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2024-08-07</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2024-08-21</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2024-09-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2024-09-19</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2024-10-03</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2024-10-17</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2024-10-31</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2024-11-14</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2024-11-29</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2024-12-13</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024-12-30</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025-01-15</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2025-01-30</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2025-02-13</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2025-02-28</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2025-03-14</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2025-03-28</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2025-04-11</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2025-04-28</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2025-05-12</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2025-05-27</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2025-06-10</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2025-06-25</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2025-07-10</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2025-07-24</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2025-08-07</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2025-08-21</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2025-09-05</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2025-09-19</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2025-10-03</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2025-10-17</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2025-10-31</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2025-11-14</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2025-12-01</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2025-12-15</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2025-12-30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>factor_LE_cum_ret!$G$2:$G$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>-6.6492098658782472E-3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-9.4765204870408404E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-9.2760788803368799E-3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.3693351103339579E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-8.3806745312589026E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-2.8888681494689821E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4.0788193126034544E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.9210507467645851E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-3.6248563572143337E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-3.8633706232406029E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-2.862583808071462E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-2.9903708791509279E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-4.3027812626151192E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-4.043814109139876E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-4.0109125574621318E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-3.9855782810674027E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-3.1339450862249318E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-3.0518177035421808E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-3.5115972974140368E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-3.0429003208978681E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-3.689525016251971E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-3.6178772750385502E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-5.2491609949007922E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-4.9367468130003811E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-3.725730445839559E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-3.5043226088683148E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-4.8166891547642199E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-5.0333778264734293E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-4.8485466931537768E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-4.668184310189416E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-3.7071441764757178E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-3.021863198073527E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-2.8652673352084549E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-3.4466012795961398E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-3.3603940200716657E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-3.068219598230337E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-4.4848690952327692E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-6.5052542539415059E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-5.4479627757443749E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-4.62405514763915E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-4.5815822615185582E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-5.1330408586274578E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-5.4420044017099878E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-5.3510020208440867E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-3.7664457801433127E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-4.5895696771893868E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-5.5403190326306251E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-6.5028570741751279E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-6.2273490957130313E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-5.8570393636402929E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-6.0747231864913931E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-5.5510829833069757E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-6.0694692949387667E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-5.9955168515900333E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-6.2244113722363381E-2</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-5.7756578095778277E-2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-4.7608811847379202E-2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-5.6527863913115588E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-5.2511597017097622E-2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-6.4773454822456666E-2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-8.137948690956387E-2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-9.100456598241502E-2</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-7.69178708517122E-2</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-7.3054893326459536E-2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-8.0777512717270183E-2</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-8.7246938942306174E-2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-0.11633918911059279</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-0.1064764774851112</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-0.10886041795791181</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-0.12403563776473329</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-0.12691610436797471</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>-0.1217747979568355</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-0.1141030518764892</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-0.1197147439898526</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-0.13752852443119179</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-0C4C-4E74-A26C-F7D819994232}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$H$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>alpha007</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$A$2:$A$76</c:f>
+              <c:strCache>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>2023-01-18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2023-02-01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-02-15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023-03-02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023-03-16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023-03-30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2023-04-14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2023-04-28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2023-05-12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2023-05-26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023-06-12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2023-06-27</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2023-07-12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2023-07-26</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2023-08-09</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2023-08-23</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2023-09-07</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2023-09-21</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023-10-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2023-10-19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2023-11-02</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2023-11-16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2023-12-01</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023-12-15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024-01-02</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024-01-17</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2024-01-31</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2024-02-14</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2024-02-29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024-03-14</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2024-03-28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2024-04-12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2024-04-26</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024-05-10</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024-05-24</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024-06-10</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2024-06-25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2024-07-10</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2024-07-24</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2024-08-07</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2024-08-21</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2024-09-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2024-09-19</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2024-10-03</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2024-10-17</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2024-10-31</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2024-11-14</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2024-11-29</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2024-12-13</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024-12-30</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025-01-15</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2025-01-30</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2025-02-13</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2025-02-28</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2025-03-14</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2025-03-28</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2025-04-11</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2025-04-28</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2025-05-12</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2025-05-27</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2025-06-10</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2025-06-25</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2025-07-10</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2025-07-24</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2025-08-07</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2025-08-21</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2025-09-05</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2025-09-19</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2025-10-03</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2025-10-17</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2025-10-31</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2025-11-14</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2025-12-01</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2025-12-15</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2025-12-30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>factor_LE_cum_ret!$H$2:$H$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="75"/>
+                <c:pt idx="1">
+                  <c:v>-8.3766365702374612E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.2051285584429081E-4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1.691430146338169E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-7.6283334777785705E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-8.085728346105181E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-7.3508981370759341E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-8.5567216764736664E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-0.1109312090780908</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-0.13004275462240819</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-0.1240429798201603</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-0.1270913998293822</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-0.1244133346459738</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-0.1261353650610901</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-0.13128133685015159</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-0.14104239302463209</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-0.1277056665486985</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-0.1178482781884136</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-0.1208262752607767</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-0.11784524858657421</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-0.115995916424549</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-0.1101993629282628</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-0.1075709314622811</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-9.9395349394787558E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-0.10234253216570011</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-0.1190423312153677</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-0.1125689670226095</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-0.1206934488291113</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-0.10976430852619209</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-0.1032364247712033</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-0.11379203515392999</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-0.10976005297223471</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-0.1133469079845674</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-0.1263301253128877</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-0.13291835182781611</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-0.14290913155888921</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0.1491653458571657</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-0.13652484091438941</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.13325584432237589</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-0.102750443971194</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-8.5479054370839358E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-7.9561709043553197E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-8.4462266015813525E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-8.7142837309395316E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-9.1476023458182842E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-0.1220719468051811</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-0.102514402224698</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-0.11176965521944129</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-0.1187588437882028</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-0.12102774775186349</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-0.10842463298081161</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-0.1168682063202313</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-0.1134148216974887</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-0.12535259366562551</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-0.1205875252685437</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-0.12778719421711371</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-0.1154024093208544</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-0.12986144592731461</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-0.1310815207942555</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-0.13418099344409029</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-0.14157760068668529</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-0.14405089279545391</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-0.14165710852376531</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-0.1433487707157102</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-0.13917320990850979</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-0.15250919397048121</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-0.16823690658185969</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-0.1703618425341272</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-0.17686385837210639</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-0.18483203507363929</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-0.17031907127901999</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>-0.18136426813828441</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-0.17693011111527279</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-0.17724732898262041</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-0.17998838881927659</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-0C4C-4E74-A26C-F7D819994232}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$I$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>alpha008</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$A$2:$A$76</c:f>
+              <c:strCache>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>2023-01-18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2023-02-01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-02-15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023-03-02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023-03-16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023-03-30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2023-04-14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2023-04-28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2023-05-12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2023-05-26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023-06-12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2023-06-27</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2023-07-12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2023-07-26</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2023-08-09</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2023-08-23</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2023-09-07</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2023-09-21</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023-10-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2023-10-19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2023-11-02</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2023-11-16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2023-12-01</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023-12-15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024-01-02</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024-01-17</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2024-01-31</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2024-02-14</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2024-02-29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024-03-14</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2024-03-28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2024-04-12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2024-04-26</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024-05-10</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024-05-24</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024-06-10</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2024-06-25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2024-07-10</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2024-07-24</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2024-08-07</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2024-08-21</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2024-09-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2024-09-19</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2024-10-03</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2024-10-17</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2024-10-31</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2024-11-14</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2024-11-29</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2024-12-13</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024-12-30</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025-01-15</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2025-01-30</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2025-02-13</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2025-02-28</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2025-03-14</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2025-03-28</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2025-04-11</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2025-04-28</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2025-05-12</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2025-05-27</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2025-06-10</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2025-06-25</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2025-07-10</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2025-07-24</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2025-08-07</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2025-08-21</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2025-09-05</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2025-09-19</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2025-10-03</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2025-10-17</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2025-10-31</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2025-11-14</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2025-12-01</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2025-12-15</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2025-12-30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>factor_LE_cum_ret!$I$2:$I$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="75"/>
+                <c:pt idx="1">
+                  <c:v>-5.2987686128550537E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.224201801546021E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-6.4507442721287722E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-5.3032094194452872E-3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.7590832064824371E-3</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-5.7488370145671874E-3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1.106368390291668E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-5.069224237591019E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-5.5866424640683587E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-6.3380885455057823E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-5.0057738718152563E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-5.6714243986697672E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-5.3610216630634699E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-5.5096786049300461E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-5.8492956024557508E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-5.2010157242780242E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-3.7450086686277813E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-3.2358166624474327E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-3.8826695784538789E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-4.6875541293397098E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-4.5029058224084872E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-2.524935678430729E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-1.5514266146091971E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-3.3687007852540307E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-4.0886047826073857E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-2.8745475278402322E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-2.607817398595003E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-2.0733325570989839E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-1.8018822547690161E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-1.1041777649636869E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-1.7419925450623212E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-2.2605865653290699E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-3.3500411672807602E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-3.110631640253703E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-3.7507243811727653E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-3.852474489806601E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-7.8260178520002111E-3</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-1.4493268443160351E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-2.0307937864565421E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-3.482361169584558E-3</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>7.3096280180808826E-3</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-1.7808474251900239E-3</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1.334591837254262E-4</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>9.1467554160029607E-4</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-1.514715137267086E-3</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.151994820295821E-3</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8.5038008565145873E-3</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1.855769185942213E-3</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-1.7214727167101599E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-2.606768124027925E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-3.2391112344676072E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-3.8959002809485173E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-6.0600572730150397E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-4.6881180960347428E-2</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-6.3484173050882386E-2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-6.2526929916456697E-2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-6.7708717840940014E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-5.8697202169048057E-2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-6.1040357355460428E-2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-6.9545361949334694E-2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-5.582920423940585E-2</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-6.7685490061500042E-2</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-6.4289101202389176E-2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-5.6806512158914191E-2</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-5.7484126564186562E-2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-8.0966400530914195E-2</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-8.5955149185201085E-2</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-9.0009069645407669E-2</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-8.6968384773470797E-2</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-8.7598130139925678E-2</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>-9.3054755356156482E-2</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-0.106157015643776</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-0.10450035934539539</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-0.1115015419719083</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-0C4C-4E74-A26C-F7D819994232}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$J$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>alpha009</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$A$2:$A$76</c:f>
+              <c:strCache>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>2023-01-18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2023-02-01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-02-15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023-03-02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023-03-16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023-03-30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2023-04-14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2023-04-28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2023-05-12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2023-05-26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023-06-12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2023-06-27</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2023-07-12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2023-07-26</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2023-08-09</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2023-08-23</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2023-09-07</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2023-09-21</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023-10-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2023-10-19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2023-11-02</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2023-11-16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2023-12-01</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023-12-15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024-01-02</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024-01-17</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2024-01-31</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2024-02-14</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2024-02-29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024-03-14</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2024-03-28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2024-04-12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2024-04-26</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024-05-10</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024-05-24</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024-06-10</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2024-06-25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2024-07-10</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2024-07-24</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2024-08-07</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2024-08-21</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2024-09-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2024-09-19</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2024-10-03</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2024-10-17</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2024-10-31</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2024-11-14</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2024-11-29</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2024-12-13</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024-12-30</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025-01-15</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2025-01-30</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2025-02-13</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2025-02-28</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2025-03-14</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2025-03-28</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2025-04-11</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2025-04-28</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2025-05-12</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2025-05-27</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2025-06-10</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2025-06-25</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2025-07-10</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2025-07-24</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2025-08-07</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2025-08-21</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2025-09-05</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2025-09-19</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2025-10-03</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2025-10-17</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2025-10-31</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2025-11-14</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2025-12-01</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2025-12-15</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2025-12-30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>factor_LE_cum_ret!$J$2:$J$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>-1.1190627002792721E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-8.6863303531504732E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.226970241507019E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.6413390565063253E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5169100132586429E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2.1269659772868769E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2.1178778706644859E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2.460677466252514E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2.538366944423931E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2.193650981599626E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.3130859882730889E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.159323815110659E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.6229633312156549E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.6900154859927481E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.9469970799081988E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.255884672646857E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.245638464480847E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.6756960706857171E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.3765021248828511E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2.3977369376297908E-3</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6.8713028716989033E-3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-3.859402800134526E-3</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>7.7285450047184234E-3</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7.7479159600102321E-3</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1.128017927652825E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1.369466226692539E-3</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1.2328987880034781E-3</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.6730882590155822E-3</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.7684086502194352E-3</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-1.5311948238640349E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-1.314476806820741E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-2.0432190566206381E-3</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-4.0415193644699476E-3</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1.8268886837982778E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-2.5060344948947271E-3</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-1.071947450519295E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-2.4089326960455629E-2</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-3.4840969100466301E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-2.6811475121541691E-2</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-4.470706636971733E-2</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-5.7385019802630673E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-6.1435713998591927E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-6.0741166496702137E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-6.8339508511687352E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-7.5690178255761187E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-5.4938505080485138E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-6.3220335319930099E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-3.3853991090264657E-2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-2.7686062827456451E-2</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-3.7051883238271577E-2</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-4.1361540120708473E-2</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-6.0620851099859707E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-6.2808975697074887E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-7.8134323717159226E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-9.6071953618360406E-2</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-8.7054655099570999E-2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-7.2798929732385109E-2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-8.0564063146253861E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-8.558378697646829E-2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-8.0211088927442997E-2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-8.1546624528969658E-2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-8.5560167284619237E-2</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-8.1251685163537091E-2</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-7.9337990133162561E-2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-6.5423582809878034E-2</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-5.0494025910472917E-2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-5.2276152488774152E-2</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-6.3222852574043364E-2</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-6.3215498592362751E-2</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-7.4839946292140525E-2</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-8.2384882426955519E-2</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>-9.4913986934246908E-2</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-9.470430529137408E-2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-9.4785662340633903E-2</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-0.10599636325871629</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-0C4C-4E74-A26C-F7D819994232}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$K$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>alpha010</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>factor_LE_cum_ret!$A$2:$A$76</c:f>
+              <c:strCache>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>2023-01-18</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2023-02-01</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2023-02-15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2023-03-02</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2023-03-16</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2023-03-30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2023-04-14</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2023-04-28</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2023-05-12</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2023-05-26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2023-06-12</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2023-06-27</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2023-07-12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2023-07-26</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2023-08-09</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2023-08-23</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2023-09-07</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2023-09-21</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2023-10-05</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2023-10-19</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2023-11-02</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2023-11-16</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2023-12-01</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2023-12-15</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2024-01-02</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2024-01-17</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2024-01-31</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2024-02-14</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2024-02-29</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2024-03-14</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2024-03-28</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2024-04-12</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2024-04-26</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2024-05-10</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2024-05-24</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2024-06-10</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2024-06-25</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2024-07-10</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2024-07-24</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2024-08-07</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2024-08-21</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2024-09-05</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2024-09-19</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2024-10-03</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2024-10-17</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2024-10-31</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2024-11-14</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2024-11-29</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2024-12-13</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2024-12-30</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2025-01-15</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2025-01-30</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2025-02-13</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2025-02-28</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2025-03-14</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2025-03-28</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2025-04-11</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2025-04-28</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2025-05-12</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2025-05-27</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2025-06-10</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2025-06-25</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2025-07-10</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2025-07-24</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2025-08-07</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2025-08-21</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2025-09-05</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2025-09-19</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2025-10-03</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2025-10-17</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2025-10-31</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2025-11-14</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2025-12-01</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2025-12-15</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2025-12-30</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>factor_LE_cum_ret!$K$2:$K$76</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="75"/>
+                <c:pt idx="0">
+                  <c:v>-1.1190627002792721E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-8.9767486208404135E-3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1.255907088718222E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4.8410711445543431E-3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.1344237510905851E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.910437606030357E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.308143315692134E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.376485606293754E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.4008921162303119E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.6333180119833871E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1.9260314659520938E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1.17071121238177E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.4851059657111421E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3.2450085545127523E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3.7093653638321733E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2.5436866982837762E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>7.605121791932179E-3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2.6630604892122989E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2.609194614156363E-2</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.8065143566911909E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.7044433760621278E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5.2751183062227147E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.5979645458392497E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.3412731392265869E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.7070003669106741E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>3.6808544419624667E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>3.0019832325141941E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3.7673938298563359E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>3.2628241863322138E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1.235011250506601E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.0710174886203751E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>3.168143687019187E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.7522974236099621E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4.0239069742325162E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.8656187710920159E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2.2530932709788901E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>6.3631209349339626E-3</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-1.391851091616614E-2</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-2.255466553057639E-3</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-9.0150734989800085E-3</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-3.2698219385745353E-2</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-3.8251065819613572E-2</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-4.2160618925831228E-2</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-4.8880179551139318E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-5.1670273691150292E-2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-3.3757704861404947E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-3.5153080806186177E-2</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-2.4321068562318531E-3</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>7.0611106404265822E-3</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-2.6394121479251802E-3</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-9.5583138548813729E-3</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-2.945656041864397E-2</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-3.0995136173719962E-2</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-4.684071768933229E-2</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-5.4729600724017557E-2</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-4.455939998405245E-2</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-2.964010730725786E-2</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-1.9419734756781382E-2</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-1.8392139140109291E-2</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-1.7531086782446859E-2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-1.773445122434425E-2</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-1.3719241984811109E-2</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-9.0722735783086428E-3</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-1.1524087306229339E-2</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>9.0768211442091573E-3</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1.9265479977044642E-2</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-6.7394064989033664E-3</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-1.7757536883829309E-2</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-1.1893932456847001E-2</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-1.87344204008878E-2</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-2.3819648334638011E-2</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>-3.6924358967461053E-2</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>-3.9082600373111058E-2</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>-3.8402120276237912E-2</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>-4.0564165788631201E-2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-0C4C-4E74-A26C-F7D819994232}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="195634128"/>
+        <c:axId val="195633648"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="195634128"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="195633648"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="195633648"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="195634128"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
   <c:roundedCorners val="1"/>
   <c:style val="2"/>
   <c:chart>
@@ -15631,7 +20879,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -20919,7 +26167,563 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -21504,6 +27308,42 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>250824</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>165099</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9521E32B-A1EE-5F7D-7A56-05C48D423729}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -21542,16 +27382,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>168274</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>85724</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>76199</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>469900</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -21867,8 +27707,9 @@
   <dimension ref="A1:Q11"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="11" max="11" width="12.7265625" customWidth="1"/>
+    <col min="11" max="11" width="21.36328125" customWidth="1"/>
     <col min="12" max="12" width="12.6328125" customWidth="1"/>
+    <col min="13" max="13" width="13.7265625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
